--- a/core/src/main/resources/baseFiles/excel/RawXL/Reports.xlsx
+++ b/core/src/main/resources/baseFiles/excel/RawXL/Reports.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EF214EF-3BFB-40FB-A7EC-37BDA2859A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{EDD5D14D-B0D8-4A16-98F2-AF3F46E1EA6C}"/>
+    <workbookView windowWidth="24680" windowHeight="14520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="tocheck" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="216">
   <si>
     <t>Firm</t>
   </si>
@@ -45,28 +37,817 @@
   </si>
   <si>
     <t>Lawyers Registered</t>
+  </si>
+  <si>
+    <t>AJU Kim Chang &amp; Lee</t>
+  </si>
+  <si>
+    <t>4min 0</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Tanner DeWitt</t>
+  </si>
+  <si>
+    <t>Global Law Office</t>
+  </si>
+  <si>
+    <t>Duan &amp; Duan</t>
+  </si>
+  <si>
+    <t>Lee &amp; Ko</t>
+  </si>
+  <si>
+    <t>TAN Law</t>
+  </si>
+  <si>
+    <t>ONC</t>
+  </si>
+  <si>
+    <t>Jingtian &amp; Gongcheng</t>
+  </si>
+  <si>
+    <t>Chance Bridge</t>
+  </si>
+  <si>
+    <t>Haiwen</t>
+  </si>
+  <si>
+    <t>Balter, Guth, Aloni &amp; Co</t>
+  </si>
+  <si>
+    <t>3min 59</t>
+  </si>
+  <si>
+    <t>Hai Run</t>
+  </si>
+  <si>
+    <t>3min 53</t>
+  </si>
+  <si>
+    <t>Lipa Meir &amp; Co</t>
+  </si>
+  <si>
+    <t>3min 4</t>
+  </si>
+  <si>
+    <t>JIPYONG</t>
+  </si>
+  <si>
+    <t>3min 3</t>
+  </si>
+  <si>
+    <t>Shoob &amp; Co</t>
+  </si>
+  <si>
+    <t>3min 0</t>
+  </si>
+  <si>
+    <t>Lanbai Law</t>
+  </si>
+  <si>
+    <t>Boase Cohen &amp; Collins</t>
+  </si>
+  <si>
+    <t>2min 54</t>
+  </si>
+  <si>
+    <t>TA Law</t>
+  </si>
+  <si>
+    <t>C&amp;T Partners</t>
+  </si>
+  <si>
+    <t>2min 49</t>
+  </si>
+  <si>
+    <t>Saga Legal</t>
+  </si>
+  <si>
+    <t>2min 30</t>
+  </si>
+  <si>
+    <t>Hylands</t>
+  </si>
+  <si>
+    <t>2min 16</t>
+  </si>
+  <si>
+    <t>Corrs</t>
+  </si>
+  <si>
+    <t>2min 2</t>
+  </si>
+  <si>
+    <t>Aquinas Law Alliance</t>
+  </si>
+  <si>
+    <t>2min 1</t>
+  </si>
+  <si>
+    <t>Hui Zhong</t>
+  </si>
+  <si>
+    <t>1min 59</t>
+  </si>
+  <si>
+    <t>Maheshwari &amp; Co</t>
+  </si>
+  <si>
+    <t>1min 53</t>
+  </si>
+  <si>
+    <t>Shook Lin &amp; Bok</t>
+  </si>
+  <si>
+    <t>1min 47</t>
+  </si>
+  <si>
+    <t>YKVN</t>
+  </si>
+  <si>
+    <t>AECO</t>
+  </si>
+  <si>
+    <t>1min 45</t>
+  </si>
+  <si>
+    <t>LHAG</t>
+  </si>
+  <si>
+    <t>1min 44</t>
+  </si>
+  <si>
+    <t>Remfry &amp; Sagar</t>
+  </si>
+  <si>
+    <t>1min 40</t>
+  </si>
+  <si>
+    <t>Domnern Somgiat &amp; Boonma</t>
+  </si>
+  <si>
+    <t>1min 37</t>
+  </si>
+  <si>
+    <t>Adnan Sundra &amp; Low</t>
+  </si>
+  <si>
+    <t>Tian Yuan</t>
+  </si>
+  <si>
+    <t>Kim Chang &amp; Lee</t>
+  </si>
+  <si>
+    <t>1min 33</t>
+  </si>
+  <si>
+    <t>Desai &amp; Diwanji</t>
+  </si>
+  <si>
+    <t>1min 23</t>
+  </si>
+  <si>
+    <t>Anand &amp; Anand</t>
+  </si>
+  <si>
+    <t>Frasers</t>
+  </si>
+  <si>
+    <t>1min 18</t>
+  </si>
+  <si>
+    <t>RIAA Barker Gillette</t>
+  </si>
+  <si>
+    <t>1min 13</t>
+  </si>
+  <si>
+    <t>Gan Lee &amp; Tan</t>
+  </si>
+  <si>
+    <t>1min 11</t>
+  </si>
+  <si>
+    <t>SG &amp; Co Lawyers</t>
+  </si>
+  <si>
+    <t>1min 9</t>
+  </si>
+  <si>
+    <t>Wong Partnership</t>
+  </si>
+  <si>
+    <t>1min 7</t>
+  </si>
+  <si>
+    <t>FGE Ebrahim Hosain</t>
+  </si>
+  <si>
+    <t>1min 4</t>
+  </si>
+  <si>
+    <t>William Hendrik &amp; Siregar Djojonegoro</t>
+  </si>
+  <si>
+    <t>1min 3</t>
+  </si>
+  <si>
+    <t>JTJB International Lawyers</t>
+  </si>
+  <si>
+    <t>1min 1</t>
+  </si>
+  <si>
+    <t>ALMT Legal</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Deheheng Law</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Al Yaqout &amp; Al Fouzan Legal</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>LS Horizon</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Asia Liuh IP</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>VILAF</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Bun &amp; Associates</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Shardul Amarchand Mangaldas &amp; Co</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Beijing East IP</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Yoon &amp; Yang</t>
+  </si>
+  <si>
+    <t>Eldan Law</t>
+  </si>
+  <si>
+    <t>SIGNUM</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Stratage Law</t>
+  </si>
+  <si>
+    <t>S&amp;O IP</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Dhaval Vussonji &amp; Associates</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Cornelius Lane &amp; Mufti</t>
+  </si>
+  <si>
+    <t>Quiason Makalintal</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Al Alawi &amp; Co</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Manuela António</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Dhir &amp; Dhir</t>
+  </si>
+  <si>
+    <t>Hiways</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>D. L. And F. De Saram</t>
+  </si>
+  <si>
+    <t>Mohanadass Partnership</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>BLC &amp; ASSOCIATES</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Haidermota &amp; Co</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Fox And Mandal</t>
+  </si>
+  <si>
+    <t>ADCO Law</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Wrays</t>
+  </si>
+  <si>
+    <t>GKC Partners</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Sayat Zholshy &amp; Partners</t>
+  </si>
+  <si>
+    <t>LAW Partnership</t>
+  </si>
+  <si>
+    <t>Zhongzi Law</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>H-F &amp; Co</t>
+  </si>
+  <si>
+    <t>Ramdas &amp; Wong</t>
+  </si>
+  <si>
+    <t>Gross &amp; Co</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Zan Hub</t>
+  </si>
+  <si>
+    <t>SCPT</t>
+  </si>
+  <si>
+    <t>RCL Chambers Law</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Vision &amp; Associates</t>
+  </si>
+  <si>
+    <t>S Horowitz &amp; Co</t>
+  </si>
+  <si>
+    <t>Bross And Partners</t>
+  </si>
+  <si>
+    <t>Ergün Avukatlik Bürosu</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>YYC Legal</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Rajani Associates</t>
+  </si>
+  <si>
+    <t>MAQ Legal</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Vanguard Lawyers Tokyo</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Deacons</t>
+  </si>
+  <si>
+    <t>Kojima Law</t>
+  </si>
+  <si>
+    <t>AF Mpanga</t>
+  </si>
+  <si>
+    <t>Bonelli Erede</t>
+  </si>
+  <si>
+    <t>Anhad Law</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Makes &amp; Partners Law</t>
+  </si>
+  <si>
+    <t>ABS And Co</t>
+  </si>
+  <si>
+    <t>Soemadipradja &amp; Taher</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Bhandari Naqvi Riaz</t>
+  </si>
+  <si>
+    <t>Sierra Legal</t>
+  </si>
+  <si>
+    <t>M&amp;D LAW</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Bowers</t>
+  </si>
+  <si>
+    <t>FCLaw</t>
+  </si>
+  <si>
+    <t>Mohsin Tayebaly &amp; Co</t>
+  </si>
+  <si>
+    <t>Tiruchelvam Associates</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>DSKLegal</t>
+  </si>
+  <si>
+    <t>Nurmansyah &amp; Muzdalifah</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Chadha &amp; Co</t>
+  </si>
+  <si>
+    <t>Barnea And Co</t>
+  </si>
+  <si>
+    <t>MBIP</t>
+  </si>
+  <si>
+    <t>Russell McVeagh</t>
+  </si>
+  <si>
+    <t>Deutsch Miller</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>HY Leung &amp; Co</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Global Vietnam Lawyers</t>
+  </si>
+  <si>
+    <t>Helmsman</t>
+  </si>
+  <si>
+    <t>Moroğlu Arseven</t>
+  </si>
+  <si>
+    <t>Baohua Law</t>
+  </si>
+  <si>
+    <t>Doogue + George</t>
+  </si>
+  <si>
+    <t>Tommy Thomas</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>MAS Law</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Economic Laws Practice</t>
+  </si>
+  <si>
+    <t>Vellani &amp; Vellani</t>
+  </si>
+  <si>
+    <t>Malley And Co</t>
+  </si>
+  <si>
+    <t>Axis Law Chambers</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Niedermüller</t>
+  </si>
+  <si>
+    <t>LNT</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Arnold Bloch Leibler</t>
+  </si>
+  <si>
+    <t>Aequitas</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sok Siphana &amp; Associates</t>
+  </si>
+  <si>
+    <t>AC&amp;R</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Dashnyam</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>K1 Chamber</t>
+  </si>
+  <si>
+    <t>KECO Legal</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Amicus</t>
+  </si>
+  <si>
+    <t>BTG Advaya</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Samvad Partners</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>AOil</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -75,12 +856,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -90,43 +1057,329 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -175,7 +1428,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -208,26 +1461,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -260,23 +1496,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -438,36 +1657,1744 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A350BCBC-CDDB-414C-9A72-BE6A09964F3F}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C139"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="3" width="27.6640625" style="2" customWidth="1"/>
-    <col min="4" max="8" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.6634615384615" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3461538461538" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1442307692308" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.88461538461539" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="23.2" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState ref="A2:C350">
+    <sortCondition ref="C2"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="D2:F35"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <cols>
+    <col min="4" max="4" width="36.0769230769231" customWidth="1"/>
+    <col min="5" max="6" width="15.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:6">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="4:6">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="4:6">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="4:6">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="4:6">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="4:6">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="4:6">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="4:6">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="4:6">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="4:6">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="4:6">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="4:6">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="4:6">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="4:6">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="4:6">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="4:6">
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="4:6">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="4:6">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="4:6">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="4:6">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="4:6">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="4:6">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="4:6">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="4:6">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="4:6">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="4:6">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="4:6">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="4:6">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="4:6">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="4:6">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+  </sheetData>
+  <sortState ref="D2:F35">
+    <sortCondition ref="E2:E35"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>